--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_stats.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_stats.xlsx
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>0.7</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N2" t="n">
         <v>13</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N3" t="n">
         <v>13</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0.7</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N4" t="n">
         <v>13</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="D8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="E8" t="n">
         <v>0.93</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>35</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="E9" t="n">
         <v>0.7</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
         <v>35</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
         <v>0.41</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>35</v>
@@ -1606,16 +1606,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0.61</v>
       </c>
       <c r="F11" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N11" t="n">
         <v>13</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="D12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="E12" t="n">
         <v>0.86</v>
       </c>
       <c r="F12" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N12" t="n">
         <v>13</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="D13" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="E13" t="n">
         <v>0.93</v>
       </c>
       <c r="F13" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
         <v>13</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="D14" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="E14" t="n">
         <v>0.86</v>
@@ -1988,7 +1988,7 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D15" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E15" t="n">
         <v>0.93</v>
@@ -2100,7 +2100,7 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="E16" t="n">
         <v>0.7</v>
@@ -2212,7 +2212,7 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
         <v>0.78</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>13</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
         <v>0.51</v>
       </c>
       <c r="F25" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="D26" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="E26" t="n">
         <v>0.78</v>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
         <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D27" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N27" t="n">
         <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D28" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="E28" t="n">
         <v>0.78</v>
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N28" t="n">
         <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="D35" t="n">
         <v>0.97</v>
@@ -4329,7 +4329,7 @@
         <v>13</v>
       </c>
       <c r="N35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -4409,7 +4409,7 @@
         <v>0.96</v>
       </c>
       <c r="D36" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="E36" t="n">
         <v>0.93</v>
@@ -4441,7 +4441,7 @@
         <v>13</v>
       </c>
       <c r="N36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="E37" t="n">
         <v>0.86</v>
@@ -4553,7 +4553,7 @@
         <v>13</v>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="D38" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         <v>13</v>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="E39" t="n">
         <v>0.73</v>
@@ -4777,7 +4777,7 @@
         <v>13</v>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="n">
         <v>0.38</v>
@@ -4889,7 +4889,7 @@
         <v>13</v>
       </c>
       <c r="N40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D47" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="E47" t="n">
         <v>0.61</v>
@@ -5684,7 +5684,7 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -5750,10 +5750,10 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D48" t="n">
         <v>0.72</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.71</v>
       </c>
       <c r="E48" t="n">
         <v>0.86</v>
@@ -5796,7 +5796,7 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E49" t="n">
         <v>0.93</v>
@@ -5908,7 +5908,7 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="D50" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="E50" t="n">
         <v>0.93</v>
@@ -6020,7 +6020,7 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="D51" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="E51" t="n">
         <v>0.86</v>
@@ -6132,7 +6132,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="U51" t="inlineStr"/>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="D52" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="E52" t="n">
         <v>0.61</v>
@@ -6244,7 +6244,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
@@ -6982,16 +6982,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="D59" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="E59" t="n">
         <v>0.63</v>
       </c>
       <c r="F59" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7014,13 +7014,13 @@
         </is>
       </c>
       <c r="M59" t="n">
+        <v>13</v>
+      </c>
+      <c r="N59" t="n">
         <v>14</v>
       </c>
-      <c r="N59" t="n">
-        <v>13</v>
-      </c>
       <c r="O59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
@@ -7094,16 +7094,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="E60" t="n">
         <v>0.92</v>
       </c>
       <c r="F60" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7126,13 +7126,13 @@
         </is>
       </c>
       <c r="M60" t="n">
+        <v>13</v>
+      </c>
+      <c r="N60" t="n">
         <v>14</v>
       </c>
-      <c r="N60" t="n">
-        <v>13</v>
-      </c>
       <c r="O60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
@@ -7206,16 +7206,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="D61" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="E61" t="n">
         <v>0.83</v>
       </c>
       <c r="F61" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="M61" t="n">
+        <v>13</v>
+      </c>
+      <c r="N61" t="n">
         <v>14</v>
       </c>
-      <c r="N61" t="n">
-        <v>13</v>
-      </c>
       <c r="O61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -7654,10 +7654,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="D65" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="E65" t="n">
         <v>0.92</v>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N65" t="n">
         <v>13</v>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="E66" t="n">
         <v>0.83</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N66" t="n">
         <v>13</v>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="D67" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="E67" t="n">
         <v>0.51</v>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N67" t="n">
         <v>13</v>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="D68" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="E68" t="n">
         <v>0.59</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N68" t="n">
         <v>13</v>
@@ -8102,10 +8102,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="D69" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="E69" t="n">
         <v>0.91</v>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N69" t="n">
         <v>13</v>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="D70" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="E70" t="n">
         <v>0.8100000000000001</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N70" t="n">
         <v>13</v>
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D74" t="n">
         <v>0.14</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.16</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N74" t="n">
         <v>10</v>
@@ -8774,10 +8774,10 @@
         </is>
       </c>
       <c r="C75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D75" t="n">
         <v>0.21</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.23</v>
       </c>
       <c r="E75" t="n">
         <v>0.78</v>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N75" t="n">
         <v>10</v>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D76" t="n">
         <v>0.28</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.29</v>
       </c>
       <c r="E76" t="n">
         <v>0.51</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N76" t="n">
         <v>10</v>
@@ -9330,21 +9330,13 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.63</v>
-      </c>
+          <t>Alternative 1 (extraction failed)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
@@ -9362,27 +9354,17 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>13</v>
-      </c>
-      <c r="N80" t="n">
-        <v>13</v>
-      </c>
-      <c r="O80" t="n">
-        <v>20</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
@@ -9397,23 +9379,23 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Z80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>1</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -9442,21 +9424,13 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.63</v>
-      </c>
+          <t>Alternative 2 (extraction failed)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
@@ -9474,27 +9448,17 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>13</v>
-      </c>
-      <c r="N81" t="n">
-        <v>13</v>
-      </c>
-      <c r="O81" t="n">
-        <v>20</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
@@ -9509,23 +9473,23 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Z81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>1</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -9554,21 +9518,13 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.63</v>
-      </c>
+          <t>Alternative 3 (extraction failed)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
@@ -9586,27 +9542,17 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>13</v>
-      </c>
-      <c r="N82" t="n">
-        <v>13</v>
-      </c>
-      <c r="O82" t="n">
-        <v>20</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
@@ -9621,23 +9567,23 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Z82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>1</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -9670,10 +9616,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="D83" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="E83" t="n">
         <v>0.85</v>
@@ -9702,7 +9648,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N83" t="n">
         <v>13</v>
@@ -9782,10 +9728,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="D84" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="E84" t="n">
         <v>0.67</v>
@@ -9814,7 +9760,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N84" t="n">
         <v>13</v>
@@ -9894,10 +9840,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="D85" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="E85" t="n">
         <v>0.45</v>
@@ -9926,7 +9872,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N85" t="n">
         <v>13</v>
@@ -10006,16 +9952,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E86" t="n">
         <v>0.73</v>
       </c>
       <c r="F86" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10038,13 +9984,13 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O86" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
@@ -10118,16 +10064,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="E87" t="n">
         <v>0.51</v>
       </c>
       <c r="F87" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10150,13 +10096,13 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O87" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
@@ -10230,16 +10176,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="D88" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="E88" t="n">
         <v>0.23</v>
       </c>
       <c r="F88" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -10262,13 +10208,13 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O88" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
@@ -10342,16 +10288,16 @@
         </is>
       </c>
       <c r="C89" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D89" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.51</v>
       </c>
       <c r="E89" t="n">
         <v>0.93</v>
       </c>
       <c r="F89" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -10374,13 +10320,13 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N89" t="n">
         <v>13</v>
       </c>
       <c r="O89" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
@@ -10454,16 +10400,16 @@
         </is>
       </c>
       <c r="C90" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D90" t="n">
         <v>0.53</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0.54</v>
       </c>
       <c r="E90" t="n">
         <v>0.78</v>
       </c>
       <c r="F90" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -10486,13 +10432,13 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N90" t="n">
         <v>13</v>
       </c>
       <c r="O90" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
@@ -10566,7 +10512,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="D91" t="n">
         <v>0.5600000000000001</v>
@@ -10575,7 +10521,7 @@
         <v>0.61</v>
       </c>
       <c r="F91" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -10598,13 +10544,13 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N91" t="n">
         <v>13</v>
       </c>
       <c r="O91" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
@@ -10678,10 +10624,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="D92" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="E92" t="n">
         <v>0.45</v>
@@ -10710,10 +10656,10 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
@@ -10790,10 +10736,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -10822,10 +10768,10 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O93" t="n">
         <v>8</v>
@@ -10902,10 +10848,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="D94" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="E94" t="n">
         <v>0.45</v>
@@ -10934,10 +10880,10 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
@@ -11014,10 +10960,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="D95" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="E95" t="n">
         <v>0.86</v>
@@ -11046,7 +10992,7 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N95" t="n">
         <v>13</v>
@@ -11126,10 +11072,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="D96" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="E96" t="n">
         <v>0.7</v>
@@ -11158,7 +11104,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N96" t="n">
         <v>13</v>
@@ -11238,10 +11184,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="D97" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="E97" t="n">
         <v>0.51</v>
@@ -11270,7 +11216,7 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N97" t="n">
         <v>13</v>
@@ -11686,10 +11632,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="D101" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="E101" t="n">
         <v>0.86</v>
@@ -11718,10 +11664,10 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O101" t="n">
         <v>35</v>
@@ -11798,10 +11744,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="D102" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="E102" t="n">
         <v>0.7</v>
@@ -11830,10 +11776,10 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N102" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O102" t="n">
         <v>35</v>
@@ -11910,10 +11856,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="E103" t="n">
         <v>0.51</v>
@@ -11942,10 +11888,10 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O103" t="n">
         <v>35</v>
@@ -12367,7 +12313,7 @@
         <v>0.78</v>
       </c>
       <c r="F107" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -12396,7 +12342,7 @@
         <v>13</v>
       </c>
       <c r="O107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
@@ -12479,7 +12425,7 @@
         <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -12508,7 +12454,7 @@
         <v>13</v>
       </c>
       <c r="O108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
@@ -12620,7 +12566,7 @@
         <v>13</v>
       </c>
       <c r="O109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
@@ -13062,7 +13008,7 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N113" t="n">
         <v>13</v>
@@ -13174,7 +13120,7 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N114" t="n">
         <v>13</v>
@@ -13286,7 +13232,7 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N115" t="n">
         <v>13</v>
@@ -13366,10 +13312,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="D116" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="E116" t="n">
         <v>0.61</v>
@@ -13401,7 +13347,7 @@
         <v>13</v>
       </c>
       <c r="N116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
         <v>25</v>
@@ -13478,10 +13424,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="D117" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="E117" t="n">
         <v>0.86</v>
@@ -13513,7 +13459,7 @@
         <v>13</v>
       </c>
       <c r="N117" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O117" t="n">
         <v>25</v>
@@ -13590,10 +13536,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="D118" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="E118" t="n">
         <v>0.86</v>
@@ -13625,7 +13571,7 @@
         <v>13</v>
       </c>
       <c r="N118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O118" t="n">
         <v>25</v>
@@ -13711,7 +13657,7 @@
         <v>0.67</v>
       </c>
       <c r="F119" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -13740,7 +13686,7 @@
         <v>13</v>
       </c>
       <c r="O119" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
@@ -13823,7 +13769,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -13852,7 +13798,7 @@
         <v>13</v>
       </c>
       <c r="O120" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
@@ -13935,7 +13881,7 @@
         <v>0.67</v>
       </c>
       <c r="F121" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -13964,7 +13910,7 @@
         <v>13</v>
       </c>
       <c r="O121" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
@@ -14710,10 +14656,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="D128" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="E128" t="n">
         <v>0.86</v>
@@ -14745,7 +14691,7 @@
         <v>14</v>
       </c>
       <c r="N128" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="O128" t="n">
         <v>25</v>
@@ -14756,7 +14702,7 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="U128" t="inlineStr"/>
@@ -14822,10 +14768,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="D129" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E129" t="n">
         <v>0.15</v>
@@ -14857,7 +14803,7 @@
         <v>14</v>
       </c>
       <c r="N129" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="O129" t="n">
         <v>25</v>
@@ -14868,7 +14814,7 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="U129" t="inlineStr"/>
@@ -14969,7 +14915,7 @@
         <v>14</v>
       </c>
       <c r="N130" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="O130" t="n">
         <v>25</v>
@@ -14980,7 +14926,7 @@
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="U130" t="inlineStr"/>
@@ -15046,10 +14992,10 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="D131" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="E131" t="n">
         <v>0.86</v>
@@ -15078,13 +15024,13 @@
         </is>
       </c>
       <c r="M131" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N131" t="n">
         <v>13</v>
       </c>
       <c r="O131" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
@@ -15092,7 +15038,7 @@
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="U131" t="inlineStr"/>
@@ -15158,10 +15104,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E132" t="n">
         <v>0.15</v>
@@ -15190,13 +15136,13 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N132" t="n">
         <v>13</v>
       </c>
       <c r="O132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
@@ -15204,7 +15150,7 @@
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="U132" t="inlineStr"/>
@@ -15302,13 +15248,13 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N133" t="n">
         <v>13</v>
       </c>
       <c r="O133" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -15316,7 +15262,7 @@
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="U133" t="inlineStr"/>
@@ -15382,10 +15328,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="D134" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="E134" t="n">
         <v>0.76</v>
@@ -15414,7 +15360,7 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N134" t="n">
         <v>13</v>
@@ -15494,10 +15440,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="D135" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="E135" t="n">
         <v>0.93</v>
@@ -15526,7 +15472,7 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N135" t="n">
         <v>13</v>
@@ -15606,10 +15552,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="D136" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="E136" t="n">
         <v>0.67</v>
@@ -15638,7 +15584,7 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N136" t="n">
         <v>13</v>
@@ -16054,10 +16000,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="E140" t="n">
         <v>0.7</v>
@@ -16086,10 +16032,10 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N140" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O140" t="n">
         <v>25</v>
@@ -16166,10 +16112,10 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="D141" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -16198,10 +16144,10 @@
         </is>
       </c>
       <c r="M141" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N141" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O141" t="n">
         <v>25</v>
@@ -16278,10 +16224,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="D142" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="E142" t="n">
         <v>0.78</v>
@@ -16310,10 +16256,10 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N142" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O142" t="n">
         <v>25</v>
@@ -16390,10 +16336,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="D143" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="E143" t="n">
         <v>0.78</v>
@@ -16422,10 +16368,10 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O143" t="n">
         <v>3</v>
@@ -16502,10 +16448,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="D144" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -16534,10 +16480,10 @@
         </is>
       </c>
       <c r="M144" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O144" t="n">
         <v>3</v>
@@ -16614,10 +16560,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="D145" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="E145" t="n">
         <v>0.61</v>
@@ -16646,10 +16592,10 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N145" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O145" t="n">
         <v>3</v>
@@ -16726,10 +16672,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>0.7</v>
@@ -16758,7 +16704,7 @@
         </is>
       </c>
       <c r="M146" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N146" t="n">
         <v>14</v>
@@ -16838,10 +16784,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
         <v>0.93</v>
@@ -16870,7 +16816,7 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N147" t="n">
         <v>14</v>
@@ -16950,10 +16896,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="D148" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="E148" t="n">
         <v>0.78</v>
@@ -16982,7 +16928,7 @@
         </is>
       </c>
       <c r="M148" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N148" t="n">
         <v>14</v>
@@ -17071,7 +17017,7 @@
         <v>0.45</v>
       </c>
       <c r="F149" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -17100,7 +17046,7 @@
         <v>13</v>
       </c>
       <c r="O149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
@@ -17183,7 +17129,7 @@
         <v>0.93</v>
       </c>
       <c r="F150" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -17212,7 +17158,7 @@
         <v>13</v>
       </c>
       <c r="O150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
@@ -17295,7 +17241,7 @@
         <v>0.67</v>
       </c>
       <c r="F151" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -17324,7 +17270,7 @@
         <v>13</v>
       </c>
       <c r="O151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
@@ -17769,7 +17715,7 @@
         <v>13</v>
       </c>
       <c r="N155" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O155" t="n">
         <v>13</v>
@@ -17881,7 +17827,7 @@
         <v>13</v>
       </c>
       <c r="N156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O156" t="n">
         <v>13</v>
@@ -17993,7 +17939,7 @@
         <v>13</v>
       </c>
       <c r="N157" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O157" t="n">
         <v>13</v>
@@ -18438,7 +18384,7 @@
         </is>
       </c>
       <c r="M161" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N161" t="n">
         <v>13</v>
@@ -18550,7 +18496,7 @@
         </is>
       </c>
       <c r="M162" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N162" t="n">
         <v>13</v>
@@ -18630,10 +18576,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="D163" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="E163" t="n">
         <v>0.93</v>
@@ -18662,7 +18608,7 @@
         </is>
       </c>
       <c r="M163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N163" t="n">
         <v>13</v>
@@ -18774,7 +18720,7 @@
         </is>
       </c>
       <c r="M164" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N164" t="n">
         <v>13</v>
@@ -18886,7 +18832,7 @@
         </is>
       </c>
       <c r="M165" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N165" t="n">
         <v>13</v>
@@ -18998,7 +18944,7 @@
         </is>
       </c>
       <c r="M166" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N166" t="n">
         <v>13</v>
@@ -19078,10 +19024,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="D167" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="E167" t="n">
         <v>0.7</v>
@@ -19113,7 +19059,7 @@
         <v>20</v>
       </c>
       <c r="N167" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O167" t="n">
         <v>18</v>
@@ -19190,10 +19136,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D168" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="E168" t="n">
         <v>1</v>
@@ -19225,7 +19171,7 @@
         <v>20</v>
       </c>
       <c r="N168" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O168" t="n">
         <v>18</v>
@@ -19337,7 +19283,7 @@
         <v>20</v>
       </c>
       <c r="N169" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O169" t="n">
         <v>18</v>
@@ -19414,10 +19360,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="D170" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="E170" t="n">
         <v>0.67</v>
@@ -19446,7 +19392,7 @@
         </is>
       </c>
       <c r="M170" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N170" t="n">
         <v>13</v>
@@ -19526,10 +19472,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="D171" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="E171" t="n">
         <v>1</v>
@@ -19558,7 +19504,7 @@
         </is>
       </c>
       <c r="M171" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N171" t="n">
         <v>13</v>
@@ -19638,10 +19584,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="D172" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="E172" t="n">
         <v>0.67</v>
@@ -19670,7 +19616,7 @@
         </is>
       </c>
       <c r="M172" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N172" t="n">
         <v>13</v>
@@ -19750,16 +19696,16 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="D173" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="E173" t="n">
         <v>0.73</v>
       </c>
       <c r="F173" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -19782,13 +19728,13 @@
         </is>
       </c>
       <c r="M173" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N173" t="n">
         <v>13</v>
       </c>
       <c r="O173" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
@@ -19862,16 +19808,16 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="D174" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="E174" t="n">
         <v>0.92</v>
       </c>
       <c r="F174" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -19894,13 +19840,13 @@
         </is>
       </c>
       <c r="M174" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N174" t="n">
         <v>13</v>
       </c>
       <c r="O174" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
@@ -19974,16 +19920,16 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="D175" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="E175" t="n">
         <v>0.51</v>
       </c>
       <c r="F175" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -20006,13 +19952,13 @@
         </is>
       </c>
       <c r="M175" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N175" t="n">
         <v>13</v>
       </c>
       <c r="O175" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
@@ -20095,7 +20041,7 @@
         <v>0.29</v>
       </c>
       <c r="F176" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -20124,7 +20070,7 @@
         <v>13</v>
       </c>
       <c r="O176" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
@@ -20207,7 +20153,7 @@
         <v>0.7</v>
       </c>
       <c r="F177" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -20236,7 +20182,7 @@
         <v>13</v>
       </c>
       <c r="O177" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
@@ -20319,7 +20265,7 @@
         <v>0.93</v>
       </c>
       <c r="F178" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -20348,7 +20294,7 @@
         <v>13</v>
       </c>
       <c r="O178" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
@@ -20431,7 +20377,7 @@
         <v>0.7</v>
       </c>
       <c r="F179" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -20454,13 +20400,13 @@
         </is>
       </c>
       <c r="M179" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N179" t="n">
         <v>13</v>
       </c>
       <c r="O179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
@@ -20543,7 +20489,7 @@
         <v>0.93</v>
       </c>
       <c r="F180" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -20566,13 +20512,13 @@
         </is>
       </c>
       <c r="M180" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N180" t="n">
         <v>13</v>
       </c>
       <c r="O180" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
@@ -20649,13 +20595,13 @@
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="E181" t="n">
         <v>0.86</v>
       </c>
       <c r="F181" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -20678,13 +20624,13 @@
         </is>
       </c>
       <c r="M181" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N181" t="n">
         <v>13</v>
       </c>
       <c r="O181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
@@ -21468,7 +21414,7 @@
         <v>13</v>
       </c>
       <c r="O188" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -21551,7 +21497,7 @@
         <v>0.15</v>
       </c>
       <c r="F189" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -21580,7 +21526,7 @@
         <v>13</v>
       </c>
       <c r="O189" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
@@ -21663,7 +21609,7 @@
         <v>0.51</v>
       </c>
       <c r="F190" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -21692,7 +21638,7 @@
         <v>13</v>
       </c>
       <c r="O190" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
@@ -22774,10 +22720,10 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="D200" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
@@ -22809,7 +22755,7 @@
         <v>13</v>
       </c>
       <c r="N200" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O200" t="n">
         <v>25</v>
@@ -22820,7 +22766,7 @@
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="U200" t="inlineStr"/>
@@ -22886,10 +22832,10 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="D201" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="E201" t="n">
         <v>0.41</v>
@@ -22921,7 +22867,7 @@
         <v>13</v>
       </c>
       <c r="N201" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O201" t="n">
         <v>25</v>
@@ -22932,7 +22878,7 @@
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="U201" t="inlineStr"/>
@@ -22998,10 +22944,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="D202" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="E202" t="n">
         <v>0.7</v>
@@ -23033,7 +22979,7 @@
         <v>13</v>
       </c>
       <c r="N202" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O202" t="n">
         <v>25</v>
@@ -23044,7 +22990,7 @@
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
@@ -23446,10 +23392,10 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="D206" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="E206" t="n">
         <v>0.78</v>
@@ -23478,7 +23424,7 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N206" t="n">
         <v>13</v>
@@ -23558,10 +23504,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="D207" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="E207" t="n">
         <v>1</v>
@@ -23590,7 +23536,7 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N207" t="n">
         <v>13</v>
@@ -23670,10 +23616,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="D208" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="E208" t="n">
         <v>0.78</v>
@@ -23702,7 +23648,7 @@
         </is>
       </c>
       <c r="M208" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N208" t="n">
         <v>13</v>
@@ -24118,10 +24064,10 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="D212" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="E212" t="n">
         <v>1</v>
@@ -24155,7 +24101,7 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr"/>
@@ -24232,10 +24178,10 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="D213" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="E213" t="n">
         <v>0.34</v>
@@ -24269,7 +24215,7 @@
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
@@ -24346,10 +24292,10 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="D214" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="E214" t="n">
         <v>0.64</v>
@@ -24383,7 +24329,7 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr"/>
@@ -24510,7 +24456,7 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
@@ -24624,7 +24570,7 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
@@ -24738,7 +24684,7 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
@@ -24802,10 +24748,10 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="D218" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
@@ -24839,7 +24785,7 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
@@ -24916,10 +24862,10 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="E219" t="n">
         <v>0.57</v>
@@ -24953,7 +24899,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
@@ -25030,10 +24976,10 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="E220" t="n">
         <v>0.57</v>
@@ -25067,7 +25013,7 @@
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
@@ -25144,10 +25090,10 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="D221" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="E221" t="n">
         <v>1</v>
@@ -25181,7 +25127,7 @@
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
@@ -25258,10 +25204,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="D222" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="E222" t="n">
         <v>0.23</v>
@@ -25295,7 +25241,7 @@
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
@@ -25372,10 +25318,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="D223" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="E223" t="n">
         <v>0.79</v>
@@ -25409,7 +25355,7 @@
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
@@ -25486,10 +25432,10 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E224" t="n">
         <v>0.52</v>
@@ -25523,7 +25469,7 @@
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
@@ -25600,7 +25546,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -25637,7 +25583,7 @@
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
@@ -25714,7 +25660,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -25751,7 +25697,7 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
@@ -26170,7 +26116,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -26207,7 +26153,7 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
@@ -26284,7 +26230,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -26321,7 +26267,7 @@
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
@@ -26398,7 +26344,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -26435,7 +26381,7 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
@@ -26512,10 +26458,10 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="D233" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="E233" t="n">
         <v>0.57</v>
@@ -26549,7 +26495,7 @@
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
@@ -26626,10 +26572,10 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="D234" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="E234" t="n">
         <v>1</v>
@@ -26663,7 +26609,7 @@
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
@@ -26740,10 +26686,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="D235" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="E235" t="n">
         <v>0.95</v>
@@ -26777,7 +26723,7 @@
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
@@ -26854,10 +26800,10 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="D236" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E236" t="n">
         <v>0.29</v>
@@ -26891,7 +26837,7 @@
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
@@ -27005,7 +26951,7 @@
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr"/>
@@ -27082,7 +27028,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -27119,7 +27065,7 @@
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr"/>
@@ -27880,10 +27826,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="D245" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="E245" t="n">
         <v>0.26</v>
@@ -27917,7 +27863,7 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr"/>
@@ -27994,10 +27940,10 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="D246" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="E246" t="n">
         <v>0.09</v>
@@ -28031,7 +27977,7 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr"/>
@@ -28108,10 +28054,10 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="E247" t="n">
         <v>1</v>
@@ -28145,7 +28091,7 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr"/>
@@ -28222,10 +28168,10 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E248" t="n">
         <v>0.7</v>
@@ -28259,7 +28205,7 @@
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr"/>
@@ -28336,10 +28282,10 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E249" t="n">
         <v>0.83</v>
@@ -28373,7 +28319,7 @@
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr"/>
@@ -28487,7 +28433,7 @@
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr"/>
@@ -28564,10 +28510,10 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="D251" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E251" t="n">
         <v>0.31</v>
@@ -28601,7 +28547,7 @@
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr"/>
@@ -28681,7 +28627,7 @@
         <v>0</v>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E252" t="n">
         <v>1</v>
@@ -28715,7 +28661,7 @@
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr"/>
@@ -28792,10 +28738,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E253" t="n">
         <v>0.63</v>
@@ -28829,7 +28775,7 @@
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr"/>
@@ -28906,10 +28852,10 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="D254" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="E254" t="n">
         <v>0.73</v>
@@ -28943,7 +28889,7 @@
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr"/>
@@ -29020,10 +28966,10 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="D255" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="E255" t="n">
         <v>0.83</v>
@@ -29057,7 +29003,7 @@
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr"/>
@@ -29134,10 +29080,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="D256" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="E256" t="n">
         <v>1</v>
@@ -29171,7 +29117,7 @@
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr"/>
@@ -29248,10 +29194,10 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="D257" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="E257" t="n">
         <v>0.89</v>
@@ -29285,7 +29231,7 @@
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
@@ -29298,7 +29244,7 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
@@ -29362,10 +29308,10 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="D258" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E258" t="n">
         <v>0.52</v>
@@ -29399,7 +29345,7 @@
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr"/>
@@ -29412,7 +29358,7 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="W258" t="inlineStr">
@@ -29476,10 +29422,10 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="D259" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E259" t="n">
         <v>0.65</v>
@@ -29513,7 +29459,7 @@
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr"/>
@@ -29526,7 +29472,7 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
@@ -29640,7 +29586,7 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="W260" t="inlineStr">
@@ -29754,7 +29700,7 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
@@ -29868,7 +29814,7 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="W262" t="inlineStr">
@@ -29932,7 +29878,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -29969,7 +29915,7 @@
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr"/>
@@ -30046,10 +29992,10 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="D264" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E264" t="n">
         <v>0.38</v>
@@ -30083,7 +30029,7 @@
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr"/>
@@ -30160,7 +30106,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -30197,7 +30143,7 @@
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr"/>
@@ -30274,10 +30220,10 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="D266" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="E266" t="n">
         <v>0.79</v>
@@ -30311,7 +30257,7 @@
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr"/>
@@ -30388,10 +30334,10 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>0.82</v>
+        <v>0.36</v>
       </c>
       <c r="D267" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="E267" t="n">
         <v>1</v>
@@ -30425,7 +30371,7 @@
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr"/>
@@ -30502,10 +30448,10 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="D268" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="E268" t="n">
         <v>0.74</v>
@@ -30539,7 +30485,7 @@
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr"/>
@@ -30958,10 +30904,10 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="D272" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="E272" t="n">
         <v>0.54</v>
@@ -30995,7 +30941,7 @@
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr"/>
@@ -31072,10 +31018,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="D273" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="E273" t="n">
         <v>0.74</v>
@@ -31109,7 +31055,7 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr"/>
@@ -31186,10 +31132,10 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="D274" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="E274" t="n">
         <v>1</v>
@@ -31223,7 +31169,7 @@
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr"/>
@@ -31300,7 +31246,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -31337,7 +31283,7 @@
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr"/>
@@ -31414,10 +31360,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="D276" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
         <v>0.25</v>
@@ -31451,7 +31397,7 @@
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr"/>
@@ -31565,7 +31511,7 @@
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr"/>
@@ -32668,10 +32614,10 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="D287" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E287" t="n">
         <v>0.51</v>
@@ -32705,7 +32651,7 @@
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr"/>
@@ -32782,10 +32728,10 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="D288" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E288" t="n">
         <v>0.79</v>
@@ -32819,7 +32765,7 @@
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr"/>
@@ -32896,10 +32842,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="D289" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E289" t="n">
         <v>1</v>
@@ -32933,7 +32879,7 @@
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr"/>
@@ -33744,7 +33690,7 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="W296" t="inlineStr">
@@ -33858,7 +33804,7 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
@@ -33972,7 +33918,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="W298" t="inlineStr">
@@ -35062,10 +35008,10 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="D308" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="E308" t="n">
         <v>0.85</v>
@@ -35099,7 +35045,7 @@
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q308" t="inlineStr"/>
       <c r="R308" t="inlineStr"/>
@@ -35112,7 +35058,7 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="W308" t="inlineStr">
@@ -35176,10 +35122,10 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="D309" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E309" t="n">
         <v>0.71</v>
@@ -35213,7 +35159,7 @@
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q309" t="inlineStr"/>
       <c r="R309" t="inlineStr"/>
@@ -35226,7 +35172,7 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="W309" t="inlineStr">
@@ -35290,10 +35236,10 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="D310" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="E310" t="n">
         <v>1</v>
@@ -35327,7 +35273,7 @@
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q310" t="inlineStr"/>
       <c r="R310" t="inlineStr"/>
@@ -35340,7 +35286,7 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="W310" t="inlineStr">
@@ -35746,10 +35692,10 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="D314" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="E314" t="n">
         <v>0.63</v>
@@ -35783,7 +35729,7 @@
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q314" t="inlineStr"/>
       <c r="R314" t="inlineStr"/>
@@ -35860,10 +35806,10 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="D315" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="E315" t="n">
         <v>0.7</v>
@@ -35897,7 +35843,7 @@
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q315" t="inlineStr"/>
       <c r="R315" t="inlineStr"/>
@@ -35974,10 +35920,10 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="D316" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="E316" t="n">
         <v>0.51</v>
@@ -36011,7 +35957,7 @@
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q316" t="inlineStr"/>
       <c r="R316" t="inlineStr"/>
@@ -36088,10 +36034,10 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="D317" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="E317" t="n">
         <v>0.91</v>
@@ -36125,7 +36071,7 @@
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="Q317" t="inlineStr"/>
       <c r="R317" t="inlineStr"/>
@@ -36202,10 +36148,10 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="D318" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="E318" t="n">
         <v>0.78</v>
@@ -36239,7 +36185,7 @@
       <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="Q318" t="inlineStr"/>
       <c r="R318" t="inlineStr"/>
@@ -36316,10 +36262,10 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="D319" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="E319" t="n">
         <v>0.96</v>
@@ -36353,7 +36299,7 @@
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="Q319" t="inlineStr"/>
       <c r="R319" t="inlineStr"/>
@@ -36430,7 +36376,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="D320" t="n">
         <v>0</v>
@@ -36467,7 +36413,7 @@
       <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q320" t="inlineStr"/>
       <c r="R320" t="inlineStr"/>
@@ -36581,7 +36527,7 @@
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q321" t="inlineStr"/>
       <c r="R321" t="inlineStr"/>
@@ -36695,7 +36641,7 @@
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q322" t="inlineStr"/>
       <c r="R322" t="inlineStr"/>
@@ -37114,10 +37060,10 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="D326" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="E326" t="n">
         <v>0.82</v>
@@ -37151,7 +37097,7 @@
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q326" t="inlineStr"/>
       <c r="R326" t="inlineStr"/>
@@ -37164,7 +37110,7 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="W326" t="inlineStr">
@@ -37228,10 +37174,10 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D327" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="E327" t="n">
         <v>0.58</v>
@@ -37265,7 +37211,7 @@
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q327" t="inlineStr"/>
       <c r="R327" t="inlineStr"/>
@@ -37278,7 +37224,7 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="W327" t="inlineStr">
@@ -37342,10 +37288,10 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="D328" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="E328" t="n">
         <v>0.9399999999999999</v>
@@ -37379,7 +37325,7 @@
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q328" t="inlineStr"/>
       <c r="R328" t="inlineStr"/>
@@ -37392,7 +37338,7 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="W328" t="inlineStr">
@@ -38140,10 +38086,10 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="D335" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E335" t="n">
         <v>0.43</v>
@@ -38177,7 +38123,7 @@
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q335" t="inlineStr"/>
       <c r="R335" t="inlineStr"/>
@@ -38254,7 +38200,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="D336" t="n">
         <v>0</v>
@@ -38291,7 +38237,7 @@
       <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q336" t="inlineStr"/>
       <c r="R336" t="inlineStr"/>
@@ -38368,7 +38314,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="D337" t="n">
         <v>0</v>
@@ -38405,7 +38351,7 @@
       <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q337" t="inlineStr"/>
       <c r="R337" t="inlineStr"/>
@@ -38482,10 +38428,10 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D338" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E338" t="n">
         <v>1</v>
@@ -38519,7 +38465,7 @@
       <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q338" t="inlineStr"/>
       <c r="R338" t="inlineStr"/>
@@ -38596,10 +38542,10 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D339" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E339" t="n">
         <v>0.55</v>
@@ -38633,7 +38579,7 @@
       <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q339" t="inlineStr"/>
       <c r="R339" t="inlineStr"/>
@@ -38710,10 +38656,10 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D340" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E340" t="n">
         <v>0.78</v>
@@ -38747,7 +38693,7 @@
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q340" t="inlineStr"/>
       <c r="R340" t="inlineStr"/>
@@ -38824,10 +38770,10 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="D341" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="E341" t="n">
         <v>0.38</v>
@@ -38861,7 +38807,7 @@
       <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q341" t="inlineStr"/>
       <c r="R341" t="inlineStr"/>
@@ -38938,10 +38884,10 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="D342" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E342" t="n">
         <v>1</v>
@@ -38975,7 +38921,7 @@
       <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q342" t="inlineStr"/>
       <c r="R342" t="inlineStr"/>
@@ -39052,10 +38998,10 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="D343" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E343" t="n">
         <v>0.79</v>
@@ -39089,7 +39035,7 @@
       <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q343" t="inlineStr"/>
       <c r="R343" t="inlineStr"/>
@@ -39166,10 +39112,10 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="D344" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="E344" t="n">
         <v>0.85</v>
@@ -39203,7 +39149,7 @@
       <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q344" t="inlineStr"/>
       <c r="R344" t="inlineStr"/>
@@ -39216,7 +39162,7 @@
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="W344" t="inlineStr">
@@ -39280,10 +39226,10 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="D345" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E345" t="n">
         <v>0.76</v>
@@ -39317,7 +39263,7 @@
       <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q345" t="inlineStr"/>
       <c r="R345" t="inlineStr"/>
@@ -39330,7 +39276,7 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="W345" t="inlineStr">
@@ -39394,10 +39340,10 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="D346" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="E346" t="n">
         <v>1</v>
@@ -39431,7 +39377,7 @@
       <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q346" t="inlineStr"/>
       <c r="R346" t="inlineStr"/>
@@ -39444,7 +39390,7 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="W346" t="inlineStr">
@@ -39508,10 +39454,10 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="D347" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="E347" t="n">
         <v>0.43</v>
@@ -39545,7 +39491,7 @@
       <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr"/>
       <c r="P347" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q347" t="inlineStr"/>
       <c r="R347" t="inlineStr"/>
@@ -39622,10 +39568,10 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="D348" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="E348" t="n">
         <v>1</v>
@@ -39659,7 +39605,7 @@
       <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q348" t="inlineStr"/>
       <c r="R348" t="inlineStr"/>
@@ -39736,10 +39682,10 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="D349" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="E349" t="n">
         <v>0.7</v>
@@ -39773,7 +39719,7 @@
       <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q349" t="inlineStr"/>
       <c r="R349" t="inlineStr"/>
@@ -39850,10 +39796,10 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E350" t="n">
         <v>0.43</v>
@@ -39887,7 +39833,7 @@
       <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q350" t="inlineStr"/>
       <c r="R350" t="inlineStr"/>
@@ -40001,7 +39947,7 @@
       <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q351" t="inlineStr"/>
       <c r="R351" t="inlineStr"/>
@@ -40078,7 +40024,7 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="D352" t="n">
         <v>0</v>
@@ -40115,7 +40061,7 @@
       <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q352" t="inlineStr"/>
       <c r="R352" t="inlineStr"/>
@@ -40192,10 +40138,10 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D353" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="E353" t="n">
         <v>0.78</v>
@@ -40229,7 +40175,7 @@
       <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q353" t="inlineStr"/>
       <c r="R353" t="inlineStr"/>
@@ -40306,10 +40252,10 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="D354" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E354" t="n">
         <v>0.55</v>
@@ -40343,7 +40289,7 @@
       <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q354" t="inlineStr"/>
       <c r="R354" t="inlineStr"/>
@@ -40420,10 +40366,10 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D355" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E355" t="n">
         <v>0.55</v>
@@ -40457,7 +40403,7 @@
       <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q355" t="inlineStr"/>
       <c r="R355" t="inlineStr"/>
@@ -40534,10 +40480,10 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D356" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E356" t="n">
         <v>0.59</v>
@@ -40571,7 +40517,7 @@
       <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q356" t="inlineStr"/>
       <c r="R356" t="inlineStr"/>
@@ -40648,10 +40594,10 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D357" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="E357" t="n">
         <v>0.78</v>
@@ -40685,7 +40631,7 @@
       <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q357" t="inlineStr"/>
       <c r="R357" t="inlineStr"/>
@@ -40762,10 +40708,10 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="D358" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E358" t="n">
         <v>0.63</v>
@@ -40799,7 +40745,7 @@
       <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q358" t="inlineStr"/>
       <c r="R358" t="inlineStr"/>
@@ -40876,10 +40822,10 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E359" t="n">
         <v>0.78</v>
@@ -40913,7 +40859,7 @@
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q359" t="inlineStr"/>
       <c r="R359" t="inlineStr"/>
@@ -40990,7 +40936,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
@@ -41027,7 +40973,7 @@
       <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q360" t="inlineStr"/>
       <c r="R360" t="inlineStr"/>
@@ -41104,7 +41050,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
@@ -41141,7 +41087,7 @@
       <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q361" t="inlineStr"/>
       <c r="R361" t="inlineStr"/>
@@ -41218,10 +41164,10 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D362" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E362" t="n">
         <v>0.78</v>
@@ -41255,7 +41201,7 @@
       <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q362" t="inlineStr"/>
       <c r="R362" t="inlineStr"/>
@@ -41268,7 +41214,7 @@
       </c>
       <c r="V362" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="W362" t="inlineStr">
@@ -41332,10 +41278,10 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D363" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E363" t="n">
         <v>0.47</v>
@@ -41369,7 +41315,7 @@
       <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q363" t="inlineStr"/>
       <c r="R363" t="inlineStr"/>
@@ -41382,7 +41328,7 @@
       </c>
       <c r="V363" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="W363" t="inlineStr">
@@ -41446,10 +41392,10 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D364" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E364" t="n">
         <v>1</v>
@@ -41483,7 +41429,7 @@
       <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q364" t="inlineStr"/>
       <c r="R364" t="inlineStr"/>
@@ -41496,7 +41442,7 @@
       </c>
       <c r="V364" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="W364" t="inlineStr">
@@ -41560,7 +41506,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="D365" t="n">
         <v>0</v>
@@ -41597,7 +41543,7 @@
       <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q365" t="inlineStr"/>
       <c r="R365" t="inlineStr"/>
@@ -41674,10 +41620,10 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="D366" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E366" t="n">
         <v>0.78</v>
@@ -41711,7 +41657,7 @@
       <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q366" t="inlineStr"/>
       <c r="R366" t="inlineStr"/>
@@ -41825,7 +41771,7 @@
       <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr"/>
       <c r="P367" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q367" t="inlineStr"/>
       <c r="R367" t="inlineStr"/>
@@ -42586,10 +42532,10 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="D374" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="E374" t="n">
         <v>0.46</v>
@@ -42623,7 +42569,7 @@
       <c r="N374" t="inlineStr"/>
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q374" t="inlineStr"/>
       <c r="R374" t="inlineStr"/>
@@ -42700,10 +42646,10 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="D375" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="E375" t="n">
         <v>1</v>
@@ -42737,7 +42683,7 @@
       <c r="N375" t="inlineStr"/>
       <c r="O375" t="inlineStr"/>
       <c r="P375" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q375" t="inlineStr"/>
       <c r="R375" t="inlineStr"/>
@@ -42814,10 +42760,10 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="D376" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="E376" t="n">
         <v>0.21</v>
@@ -42851,7 +42797,7 @@
       <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q376" t="inlineStr"/>
       <c r="R376" t="inlineStr"/>
@@ -42931,7 +42877,7 @@
         <v>0.85</v>
       </c>
       <c r="D377" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="E377" t="n">
         <v>0.59</v>
@@ -42965,7 +42911,7 @@
       <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr"/>
       <c r="P377" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q377" t="inlineStr"/>
       <c r="R377" t="inlineStr"/>
@@ -43042,10 +42988,10 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="D378" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="E378" t="n">
         <v>0.74</v>
@@ -43079,7 +43025,7 @@
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q378" t="inlineStr"/>
       <c r="R378" t="inlineStr"/>
@@ -43159,7 +43105,7 @@
         <v>0.85</v>
       </c>
       <c r="D379" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="E379" t="n">
         <v>1</v>
@@ -43193,7 +43139,7 @@
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
       <c r="P379" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q379" t="inlineStr"/>
       <c r="R379" t="inlineStr"/>
@@ -43270,10 +43216,10 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="D380" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E380" t="n">
         <v>0.51</v>
@@ -43307,7 +43253,7 @@
       <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q380" t="inlineStr"/>
       <c r="R380" t="inlineStr"/>
@@ -43384,10 +43330,10 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="D381" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="E381" t="n">
         <v>1</v>
@@ -43421,7 +43367,7 @@
       <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q381" t="inlineStr"/>
       <c r="R381" t="inlineStr"/>
@@ -43498,10 +43444,10 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="D382" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="E382" t="n">
         <v>0.59</v>
@@ -43535,7 +43481,7 @@
       <c r="N382" t="inlineStr"/>
       <c r="O382" t="inlineStr"/>
       <c r="P382" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q382" t="inlineStr"/>
       <c r="R382" t="inlineStr"/>
@@ -43954,10 +43900,10 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="D386" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E386" t="n">
         <v>0.53</v>
@@ -43991,7 +43937,7 @@
       <c r="N386" t="inlineStr"/>
       <c r="O386" t="inlineStr"/>
       <c r="P386" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q386" t="inlineStr"/>
       <c r="R386" t="inlineStr"/>
@@ -44068,10 +44014,10 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="D387" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E387" t="n">
         <v>0.71</v>
@@ -44105,7 +44051,7 @@
       <c r="N387" t="inlineStr"/>
       <c r="O387" t="inlineStr"/>
       <c r="P387" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q387" t="inlineStr"/>
       <c r="R387" t="inlineStr"/>
@@ -44182,10 +44128,10 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="D388" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E388" t="n">
         <v>1</v>
@@ -44219,7 +44165,7 @@
       <c r="N388" t="inlineStr"/>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q388" t="inlineStr"/>
       <c r="R388" t="inlineStr"/>
@@ -44296,10 +44242,10 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="D389" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
       <c r="E389" t="n">
         <v>0.29</v>
@@ -44333,7 +44279,7 @@
       <c r="N389" t="inlineStr"/>
       <c r="O389" t="inlineStr"/>
       <c r="P389" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q389" t="inlineStr"/>
       <c r="R389" t="inlineStr"/>
@@ -44410,10 +44356,10 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>0.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D390" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="E390" t="n">
         <v>1</v>
@@ -44447,7 +44393,7 @@
       <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q390" t="inlineStr"/>
       <c r="R390" t="inlineStr"/>
@@ -44524,10 +44470,10 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="D391" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="E391" t="n">
         <v>0.74</v>
@@ -44561,7 +44507,7 @@
       <c r="N391" t="inlineStr"/>
       <c r="O391" t="inlineStr"/>
       <c r="P391" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q391" t="inlineStr"/>
       <c r="R391" t="inlineStr"/>
@@ -44980,10 +44926,10 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D395" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="E395" t="n">
         <v>0.63</v>
@@ -45017,7 +44963,7 @@
       <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr"/>
       <c r="P395" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q395" t="inlineStr"/>
       <c r="R395" t="inlineStr"/>
@@ -45094,10 +45040,10 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="D396" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="E396" t="n">
         <v>0.74</v>
@@ -45131,7 +45077,7 @@
       <c r="N396" t="inlineStr"/>
       <c r="O396" t="inlineStr"/>
       <c r="P396" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q396" t="inlineStr"/>
       <c r="R396" t="inlineStr"/>
@@ -45208,10 +45154,10 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D397" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="E397" t="n">
         <v>1</v>
@@ -45245,7 +45191,7 @@
       <c r="N397" t="inlineStr"/>
       <c r="O397" t="inlineStr"/>
       <c r="P397" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q397" t="inlineStr"/>
       <c r="R397" t="inlineStr"/>
@@ -45322,10 +45268,10 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="D398" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="E398" t="n">
         <v>1</v>
@@ -45359,7 +45305,7 @@
       <c r="N398" t="inlineStr"/>
       <c r="O398" t="inlineStr"/>
       <c r="P398" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q398" t="inlineStr"/>
       <c r="R398" t="inlineStr"/>
@@ -45436,10 +45382,10 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="D399" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="E399" t="n">
         <v>0.47</v>
@@ -45473,7 +45419,7 @@
       <c r="N399" t="inlineStr"/>
       <c r="O399" t="inlineStr"/>
       <c r="P399" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q399" t="inlineStr"/>
       <c r="R399" t="inlineStr"/>
@@ -45550,10 +45496,10 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="D400" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="E400" t="n">
         <v>0.74</v>
@@ -45587,7 +45533,7 @@
       <c r="N400" t="inlineStr"/>
       <c r="O400" t="inlineStr"/>
       <c r="P400" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q400" t="inlineStr"/>
       <c r="R400" t="inlineStr"/>
@@ -45664,10 +45610,10 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="D401" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E401" t="n">
         <v>0.62</v>
@@ -45701,7 +45647,7 @@
       <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr"/>
       <c r="P401" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q401" t="inlineStr"/>
       <c r="R401" t="inlineStr"/>
@@ -45778,7 +45724,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="D402" t="n">
         <v>0</v>
@@ -45815,7 +45761,7 @@
       <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr"/>
       <c r="P402" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q402" t="inlineStr"/>
       <c r="R402" t="inlineStr"/>
@@ -45892,7 +45838,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="D403" t="n">
         <v>0</v>
@@ -45929,7 +45875,7 @@
       <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr"/>
       <c r="P403" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q403" t="inlineStr"/>
       <c r="R403" t="inlineStr"/>
@@ -46006,10 +45952,10 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D404" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E404" t="n">
         <v>0.55</v>
@@ -46043,7 +45989,7 @@
       <c r="N404" t="inlineStr"/>
       <c r="O404" t="inlineStr"/>
       <c r="P404" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q404" t="inlineStr"/>
       <c r="R404" t="inlineStr"/>
@@ -46120,10 +46066,10 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D405" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E405" t="n">
         <v>1</v>
@@ -46157,7 +46103,7 @@
       <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr"/>
       <c r="P405" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q405" t="inlineStr"/>
       <c r="R405" t="inlineStr"/>
@@ -46234,10 +46180,10 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="D406" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E406" t="n">
         <v>0.82</v>
@@ -46271,7 +46217,7 @@
       <c r="N406" t="inlineStr"/>
       <c r="O406" t="inlineStr"/>
       <c r="P406" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q406" t="inlineStr"/>
       <c r="R406" t="inlineStr"/>
@@ -46391,7 +46337,7 @@
         <v>1.5</v>
       </c>
       <c r="R407" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S407" t="n">
         <v>120</v>
@@ -46503,7 +46449,7 @@
         <v>1.5</v>
       </c>
       <c r="R408" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S408" t="n">
         <v>120</v>
@@ -46615,7 +46561,7 @@
         <v>1.5</v>
       </c>
       <c r="R409" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S409" t="n">
         <v>120</v>
@@ -48700,7 +48646,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="D428" t="n">
         <v>1</v>
@@ -48740,7 +48686,7 @@
       <c r="O428" t="inlineStr"/>
       <c r="P428" t="inlineStr"/>
       <c r="Q428" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R428" t="n">
         <v>50</v>
@@ -48812,16 +48758,16 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="D429" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="E429" t="n">
         <v>0.74</v>
       </c>
       <c r="F429" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -48852,7 +48798,7 @@
       <c r="O429" t="inlineStr"/>
       <c r="P429" t="inlineStr"/>
       <c r="Q429" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R429" t="n">
         <v>50</v>
@@ -48924,10 +48870,10 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="D430" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E430" t="n">
         <v>0.89</v>
@@ -48964,7 +48910,7 @@
       <c r="O430" t="inlineStr"/>
       <c r="P430" t="inlineStr"/>
       <c r="Q430" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R430" t="n">
         <v>50</v>
@@ -49412,7 +49358,7 @@
       <c r="O434" t="inlineStr"/>
       <c r="P434" t="inlineStr"/>
       <c r="Q434" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R434" t="n">
         <v>50</v>
@@ -49524,7 +49470,7 @@
       <c r="O435" t="inlineStr"/>
       <c r="P435" t="inlineStr"/>
       <c r="Q435" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R435" t="n">
         <v>50</v>
@@ -49596,10 +49542,10 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="D436" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="E436" t="n">
         <v>0.86</v>
@@ -49636,7 +49582,7 @@
       <c r="O436" t="inlineStr"/>
       <c r="P436" t="inlineStr"/>
       <c r="Q436" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R436" t="n">
         <v>50</v>
@@ -49708,10 +49654,10 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="D437" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="E437" t="n">
         <v>0.88</v>
@@ -49748,10 +49694,10 @@
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
       <c r="Q437" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R437" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S437" t="n">
         <v>120</v>
@@ -49820,7 +49766,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="D438" t="n">
         <v>0</v>
@@ -49860,10 +49806,10 @@
       <c r="O438" t="inlineStr"/>
       <c r="P438" t="inlineStr"/>
       <c r="Q438" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R438" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S438" t="n">
         <v>120</v>
@@ -49972,10 +49918,10 @@
       <c r="O439" t="inlineStr"/>
       <c r="P439" t="inlineStr"/>
       <c r="Q439" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R439" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S439" t="n">
         <v>120</v>
@@ -51428,7 +51374,7 @@
       <c r="O452" t="inlineStr"/>
       <c r="P452" t="inlineStr"/>
       <c r="Q452" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R452" t="n">
         <v>80</v>
@@ -51540,7 +51486,7 @@
       <c r="O453" t="inlineStr"/>
       <c r="P453" t="inlineStr"/>
       <c r="Q453" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R453" t="n">
         <v>80</v>
@@ -51652,7 +51598,7 @@
       <c r="O454" t="inlineStr"/>
       <c r="P454" t="inlineStr"/>
       <c r="Q454" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R454" t="n">
         <v>80</v>
@@ -52060,10 +52006,10 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="D458" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E458" t="n">
         <v>0.88</v>
@@ -52100,7 +52046,7 @@
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="inlineStr"/>
       <c r="Q458" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R458" t="n">
         <v>50</v>
@@ -52172,7 +52118,7 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D459" t="n">
         <v>0</v>
@@ -52212,7 +52158,7 @@
       <c r="O459" t="inlineStr"/>
       <c r="P459" t="inlineStr"/>
       <c r="Q459" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R459" t="n">
         <v>50</v>
@@ -52324,7 +52270,7 @@
       <c r="O460" t="inlineStr"/>
       <c r="P460" t="inlineStr"/>
       <c r="Q460" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R460" t="n">
         <v>50</v>
@@ -52439,7 +52385,7 @@
         <v>1.5</v>
       </c>
       <c r="R461" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S461" t="n">
         <v>120</v>
@@ -52551,7 +52497,7 @@
         <v>1.5</v>
       </c>
       <c r="R462" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S462" t="n">
         <v>120</v>
@@ -52663,7 +52609,7 @@
         <v>1.5</v>
       </c>
       <c r="R463" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S463" t="n">
         <v>120</v>
@@ -53111,7 +53057,7 @@
         <v>2.75</v>
       </c>
       <c r="R467" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S467" t="n">
         <v>120</v>
@@ -53223,7 +53169,7 @@
         <v>2.75</v>
       </c>
       <c r="R468" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S468" t="n">
         <v>120</v>
@@ -53335,7 +53281,7 @@
         <v>2.75</v>
       </c>
       <c r="R469" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="S469" t="n">
         <v>120</v>
@@ -53404,16 +53350,16 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="D470" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E470" t="n">
         <v>0.92</v>
       </c>
       <c r="F470" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -53444,7 +53390,7 @@
       <c r="O470" t="inlineStr"/>
       <c r="P470" t="inlineStr"/>
       <c r="Q470" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R470" t="n">
         <v>35</v>
@@ -53516,10 +53462,10 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="D471" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="E471" t="n">
         <v>0.74</v>
@@ -53556,7 +53502,7 @@
       <c r="O471" t="inlineStr"/>
       <c r="P471" t="inlineStr"/>
       <c r="Q471" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R471" t="n">
         <v>35</v>
@@ -53628,10 +53574,10 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="D472" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="E472" t="n">
         <v>1</v>
@@ -53668,7 +53614,7 @@
       <c r="O472" t="inlineStr"/>
       <c r="P472" t="inlineStr"/>
       <c r="Q472" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R472" t="n">
         <v>35</v>
@@ -56428,16 +56374,16 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>0.53</v>
+        <v>0.68</v>
       </c>
       <c r="D497" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E497" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="F497" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -56468,7 +56414,7 @@
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="inlineStr"/>
       <c r="Q497" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R497" t="n">
         <v>35</v>
@@ -56540,10 +56486,10 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="D498" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="E498" t="n">
         <v>0.68</v>
@@ -56580,7 +56526,7 @@
       <c r="O498" t="inlineStr"/>
       <c r="P498" t="inlineStr"/>
       <c r="Q498" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R498" t="n">
         <v>35</v>
@@ -56652,10 +56598,10 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="D499" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="E499" t="n">
         <v>0.9</v>
@@ -56692,7 +56638,7 @@
       <c r="O499" t="inlineStr"/>
       <c r="P499" t="inlineStr"/>
       <c r="Q499" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R499" t="n">
         <v>35</v>
@@ -59159,7 +59105,7 @@
         <v>1.5</v>
       </c>
       <c r="R521" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S521" t="n">
         <v>120</v>
@@ -59271,7 +59217,7 @@
         <v>1.5</v>
       </c>
       <c r="R522" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S522" t="n">
         <v>120</v>
@@ -59349,7 +59295,7 @@
         <v>0.9</v>
       </c>
       <c r="F523" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -59383,7 +59329,7 @@
         <v>1.5</v>
       </c>
       <c r="R523" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S523" t="n">
         <v>120</v>
@@ -60167,7 +60113,7 @@
         <v>1.5</v>
       </c>
       <c r="R530" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S530" t="n">
         <v>120</v>
@@ -60279,7 +60225,7 @@
         <v>1.5</v>
       </c>
       <c r="R531" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S531" t="n">
         <v>120</v>
@@ -60391,7 +60337,7 @@
         <v>1.5</v>
       </c>
       <c r="R532" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S532" t="n">
         <v>120</v>
@@ -61844,7 +61790,7 @@
       <c r="O545" t="inlineStr"/>
       <c r="P545" t="inlineStr"/>
       <c r="Q545" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R545" t="n">
         <v>50</v>
@@ -61916,10 +61862,10 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D546" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E546" t="n">
         <v>0.9399999999999999</v>
@@ -61956,7 +61902,7 @@
       <c r="O546" t="inlineStr"/>
       <c r="P546" t="inlineStr"/>
       <c r="Q546" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R546" t="n">
         <v>50</v>
@@ -62028,10 +61974,10 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="D547" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="E547" t="n">
         <v>0.77</v>
@@ -62068,7 +62014,7 @@
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="inlineStr"/>
       <c r="Q547" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R547" t="n">
         <v>50</v>
@@ -62476,10 +62422,10 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="D551" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="E551" t="n">
         <v>0.9399999999999999</v>
@@ -62516,7 +62462,7 @@
       <c r="O551" t="inlineStr"/>
       <c r="P551" t="inlineStr"/>
       <c r="Q551" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R551" t="n">
         <v>50</v>
@@ -62588,10 +62534,10 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="D552" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="E552" t="n">
         <v>0.68</v>
@@ -62628,7 +62574,7 @@
       <c r="O552" t="inlineStr"/>
       <c r="P552" t="inlineStr"/>
       <c r="Q552" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R552" t="n">
         <v>50</v>
@@ -62700,10 +62646,10 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="D553" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="E553" t="n">
         <v>0.89</v>
@@ -62740,7 +62686,7 @@
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr"/>
       <c r="Q553" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R553" t="n">
         <v>50</v>
@@ -63820,10 +63766,10 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="D563" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E563" t="n">
         <v>0.95</v>
@@ -63860,7 +63806,7 @@
       <c r="O563" t="inlineStr"/>
       <c r="P563" t="inlineStr"/>
       <c r="Q563" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R563" t="n">
         <v>35</v>
@@ -63932,10 +63878,10 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="D564" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="E564" t="n">
         <v>0.67</v>
@@ -63972,7 +63918,7 @@
       <c r="O564" t="inlineStr"/>
       <c r="P564" t="inlineStr"/>
       <c r="Q564" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R564" t="n">
         <v>35</v>
@@ -64044,10 +63990,10 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="D565" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="E565" t="n">
         <v>0.87</v>
@@ -64084,7 +64030,7 @@
       <c r="O565" t="inlineStr"/>
       <c r="P565" t="inlineStr"/>
       <c r="Q565" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R565" t="n">
         <v>35</v>
@@ -65207,7 +65153,7 @@
         <v>1.5</v>
       </c>
       <c r="R575" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S575" t="n">
         <v>120</v>
@@ -65319,7 +65265,7 @@
         <v>1.5</v>
       </c>
       <c r="R576" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S576" t="n">
         <v>120</v>
@@ -65431,7 +65377,7 @@
         <v>1.5</v>
       </c>
       <c r="R577" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S577" t="n">
         <v>120</v>
